--- a/Figure 6/Figure 6-O.xlsx
+++ b/Figure 6/Figure 6-O.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics7798648\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0773D16-E9F9-4A7C-9771-4ECA2A2856AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088B9824-23BB-4FF1-ACF1-E3D1A19B0ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22250" yWindow="610" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-1540" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>pBD-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,12 +43,6 @@
     <t>CON 4</t>
   </si>
   <si>
-    <t>CON 5</t>
-  </si>
-  <si>
-    <t>CON 6</t>
-  </si>
-  <si>
     <t>ETEC 1</t>
   </si>
   <si>
@@ -61,12 +55,6 @@
     <t>ETEC 4</t>
   </si>
   <si>
-    <t>ETEC 5</t>
-  </si>
-  <si>
-    <t>ETEC 6</t>
-  </si>
-  <si>
     <t>ETEC+WB800 1</t>
   </si>
   <si>
@@ -79,12 +67,6 @@
     <t>ETEC+WB800 4</t>
   </si>
   <si>
-    <t>ETEC+WB800 5</t>
-  </si>
-  <si>
-    <t>ETEC+WB800 6</t>
-  </si>
-  <si>
     <t>ETEC+WB800_KR32 1</t>
   </si>
   <si>
@@ -98,19 +80,13 @@
   </si>
   <si>
     <t>ETEC+WB800_KR32 5</t>
-  </si>
-  <si>
-    <t>ETEC+WB800_KR32 6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,6 +100,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -148,7 +130,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -429,207 +411,152 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>1.7292406130839928</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.43732635779716056</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1.783186260500691</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>0.80424206273747101</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>1.7124336984341437</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>0.59391426635164801</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>0.79663054526613053</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>9.9508350872077239E-2</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>0.30968086675204443</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>0.38072708587150306</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>0.20289674212520753</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>0.22389066164977978</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>0.24274797009845517</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>0.54272831710989566</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>0.32928695551893061</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>0.35198255726508665</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>0.35187978882929061</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.85831468687687429</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0.57371723314350676</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0.33348732892360544</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.26717356673509263</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.39915795108695651</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0.32703173518198009</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.72840131257419682</v>
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
